--- a/SGC-CKN/Excel/8f0ce4aa-025f-466b-827a-3ab1cd3b6756_Lô_CT-02_PH-70_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/8f0ce4aa-025f-466b-827a-3ab1cd3b6756_Lô_CT-02_PH-70_D800_24-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>PH-70</t>
+    <t>P-70</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/8f0ce4aa-025f-466b-827a-3ab1cd3b6756_Lô_CT-02_PH-70_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/8f0ce4aa-025f-466b-827a-3ab1cd3b6756_Lô_CT-02_PH-70_D800_24-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P-70</t>
+    <t>P11-70</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/8f0ce4aa-025f-466b-827a-3ab1cd3b6756_Lô_CT-02_PH-70_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/8f0ce4aa-025f-466b-827a-3ab1cd3b6756_Lô_CT-02_PH-70_D800_24-03-2026.xlsx
@@ -165,7 +165,7 @@
     <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">20:03
+    <t xml:space="preserve">20:53
 24/03/2026</t>
   </si>
   <si>
@@ -351,11 +351,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
@@ -367,6 +362,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,35 +520,35 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1189,7 +1189,7 @@
         <v>-2.13</v>
       </c>
       <c r="G12" s="9">
-        <v>-12.33</v>
+        <v>-12.329999999999998</v>
       </c>
       <c r="H12" s="9">
         <v>0.5</v>
@@ -1221,10 +1221,10 @@
         <v>36</v>
       </c>
       <c r="F13" s="12">
-        <v>-12.33</v>
+        <v>-12.329999999999998</v>
       </c>
       <c r="G13" s="12">
-        <v>-17.53</v>
+        <v>-17.529999999999998</v>
       </c>
       <c r="H13" s="12">
         <v>0.92</v>
@@ -1256,126 +1256,126 @@
         <v>39</v>
       </c>
       <c r="F14" s="15">
-        <v>-17.53</v>
+        <v>-17.529999999999998</v>
       </c>
       <c r="G14" s="15">
-        <v>-21.23</v>
+        <v>-28.23</v>
       </c>
       <c r="H14" s="15">
         <v>0.83</v>
       </c>
       <c r="I14" s="15">
-        <v>3.7</v>
-      </c>
-      <c r="J14" s="18">
-        <v>4.44</v>
+        <v>10.7</v>
+      </c>
+      <c r="J14" s="8">
+        <v>12.84</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19">
-        <v>-21.23</v>
-      </c>
-      <c r="G15" s="19">
+      <c r="F15" s="18">
+        <v>-28.23</v>
+      </c>
+      <c r="G15" s="18">
         <v>-32.03</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.42</v>
       </c>
-      <c r="I15" s="19">
-        <v>10.8</v>
+      <c r="I15" s="18">
+        <v>3.8</v>
       </c>
       <c r="J15" s="8">
-        <v>25.92</v>
-      </c>
-      <c r="K15" s="20" t="s">
+        <v>9.12</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>-32.03</v>
       </c>
-      <c r="G16" s="22">
-        <v>-39.53</v>
-      </c>
-      <c r="H16" s="22">
+      <c r="G16" s="21">
+        <v>-34.53</v>
+      </c>
+      <c r="H16" s="21">
         <v>0.33</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="J16" s="8">
         <v>7.5</v>
       </c>
-      <c r="J16" s="8">
-        <v>22.5</v>
-      </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="25">
-        <v>-39.53</v>
-      </c>
-      <c r="G17" s="25">
+      <c r="F17" s="24">
+        <v>-34.53</v>
+      </c>
+      <c r="G17" s="24">
         <v>-45</v>
       </c>
-      <c r="H17" s="25">
-        <v>2.8</v>
-      </c>
-      <c r="I17" s="25">
-        <v>5.47</v>
-      </c>
-      <c r="J17" s="18">
-        <v>1.95</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="H17" s="24">
+        <v>3.63</v>
+      </c>
+      <c r="I17" s="24">
+        <v>10.47</v>
+      </c>
+      <c r="J17" s="27">
+        <v>2.88</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1402,13 +1402,13 @@
         <v>-49.66</v>
       </c>
       <c r="H18" s="28">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="I18" s="28">
         <v>4.66</v>
       </c>
-      <c r="J18" s="18">
-        <v>1.75</v>
+      <c r="J18" s="27">
+        <v>2.54</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>53</v>
@@ -1653,103 +1653,103 @@
         <v>-17.53</v>
       </c>
       <c r="F5" s="15">
-        <v>-21.23</v>
+        <v>-28.23</v>
       </c>
       <c r="G5" s="15">
         <v>0.83</v>
       </c>
       <c r="H5" s="15">
-        <v>3.7</v>
-      </c>
-      <c r="I5" s="18">
-        <v>4.44</v>
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="8">
+        <v>12.84</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-21.23</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="E6" s="18">
+        <v>-28.23</v>
+      </c>
+      <c r="F6" s="18">
         <v>-32.03</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>0.42</v>
       </c>
-      <c r="H6" s="19">
-        <v>10.8</v>
+      <c r="H6" s="18">
+        <v>3.8</v>
       </c>
       <c r="I6" s="8">
-        <v>25.92</v>
+        <v>9.12</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>-32.03</v>
       </c>
-      <c r="F7" s="22">
-        <v>-39.53</v>
-      </c>
-      <c r="G7" s="22">
+      <c r="F7" s="21">
+        <v>-34.53</v>
+      </c>
+      <c r="G7" s="21">
         <v>0.33</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="8">
         <v>7.5</v>
       </c>
-      <c r="I7" s="8">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
-        <v>-39.53</v>
-      </c>
-      <c r="F8" s="25">
+      <c r="E8" s="24">
+        <v>-34.53</v>
+      </c>
+      <c r="F8" s="24">
         <v>-45</v>
       </c>
-      <c r="G8" s="25">
-        <v>2.8</v>
-      </c>
-      <c r="H8" s="25">
-        <v>5.47</v>
-      </c>
-      <c r="I8" s="18">
-        <v>1.95</v>
+      <c r="G8" s="24">
+        <v>3.63</v>
+      </c>
+      <c r="H8" s="24">
+        <v>10.47</v>
+      </c>
+      <c r="I8" s="27">
+        <v>2.88</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1772,13 +1772,13 @@
         <v>-49.66</v>
       </c>
       <c r="G9" s="28">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="H9" s="28">
         <v>4.66</v>
       </c>
-      <c r="I9" s="18">
-        <v>1.75</v>
+      <c r="I9" s="27">
+        <v>2.54</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
